--- a/mortag-flow/Testplan-schema.xlsx
+++ b/mortag-flow/Testplan-schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodeo\ws\Teststraegi\NordicShop\mortag-flow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodeo\ws\nordic-shop\NordicShop\mortag-flow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{581F85AA-97CD-4F55-8822-6A06C413A2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5475489-20D0-4980-893D-9A83CF3C03BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AA035597-A4E9-4E2A-9859-DD6A2F9843BA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{AA035597-A4E9-4E2A-9859-DD6A2F9843BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t xml:space="preserve">Vecka </t>
   </si>
@@ -77,9 +77,6 @@
     <t>TC+DevOps</t>
   </si>
   <si>
-    <t>TA</t>
-  </si>
-  <si>
     <t>TBC</t>
   </si>
   <si>
@@ -96,6 +93,12 @@
   </si>
   <si>
     <t>TBDA+ SÄKspec</t>
+  </si>
+  <si>
+    <t>TABD</t>
+  </si>
+  <si>
+    <t>TABCD</t>
   </si>
 </sst>
 </file>
@@ -523,20 +526,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0932B16-92C3-47DC-BBD0-5CE3859515A1}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="41.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="41.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,7 +580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -598,12 +601,14 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
@@ -617,18 +622,20 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -638,7 +645,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="66.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -647,23 +654,23 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
     </row>
-    <row r="6" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -674,17 +681,17 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -696,16 +703,16 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -718,15 +725,15 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -741,11 +748,11 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -761,7 +768,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/mortag-flow/Testplan-schema.xlsx
+++ b/mortag-flow/Testplan-schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodeo\ws\nordic-shop\NordicShop\mortag-flow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5475489-20D0-4980-893D-9A83CF3C03BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897248F9-333B-4708-AC6D-6F6F4E459256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{AA035597-A4E9-4E2A-9859-DD6A2F9843BA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t xml:space="preserve">Vecka </t>
   </si>
@@ -71,34 +71,79 @@
     <t>Go/No-Go och produktionssättning</t>
   </si>
   <si>
-    <t>TL+A-D</t>
-  </si>
-  <si>
-    <t>TC+DevOps</t>
-  </si>
-  <si>
-    <t>TBC</t>
-  </si>
-  <si>
-    <t>TC/verksamhet</t>
-  </si>
-  <si>
-    <t>TD</t>
-  </si>
-  <si>
     <t>TL</t>
   </si>
   <si>
     <t>PO +PL</t>
   </si>
   <si>
-    <t>TBDA+ SÄKspec</t>
-  </si>
-  <si>
-    <t>TABD</t>
-  </si>
-  <si>
-    <t>TABCD</t>
+    <t>DA+ SÄKspec</t>
+  </si>
+  <si>
+    <t>ACD</t>
+  </si>
+  <si>
+    <t>C+DevO</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API </t>
+  </si>
+  <si>
+    <t>tekniska tester</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAT </t>
+  </si>
+  <si>
+    <t>Test data</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>behörighet</t>
+  </si>
+  <si>
+    <t>Regrition</t>
+  </si>
+  <si>
+    <t>acd</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>C+ VS</t>
+  </si>
+  <si>
+    <t>AcD</t>
+  </si>
+  <si>
+    <t>Da+ SÄKspec</t>
+  </si>
+  <si>
+    <t>TL+ACD</t>
+  </si>
+  <si>
+    <t>TL+AcD</t>
+  </si>
+  <si>
+    <t>D+ SÄKspec</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>ACd</t>
   </si>
 </sst>
 </file>
@@ -525,18 +570,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0932B16-92C3-47DC-BBD0-5CE3859515A1}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="41.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -585,10 +631,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -607,10 +653,10 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
@@ -622,20 +668,20 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -652,19 +698,19 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="F5" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I5" s="5"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -678,20 +724,24 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="H6" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -703,10 +753,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -720,17 +770,27 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="J8" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
@@ -746,13 +806,15 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="L9" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:13" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="35" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -767,8 +829,44 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
         <v>16</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
